--- a/georgia_ev_intelligence/outputs/ragas_reports/phase4_ragas_20260504_003123.xlsx
+++ b/georgia_ev_intelligence/outputs/ragas_reports/phase4_ragas_20260504_003123.xlsx
@@ -3596,7 +3596,7 @@
         <v>229</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="70" customFormat="1" s="15">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="69.75" customFormat="1" s="15">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
